--- a/next/app/credit-application/lib/templates/credit_application_supplier_template.xlsx
+++ b/next/app/credit-application/lib/templates/credit_application_supplier_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timchen/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F69765B8-EA77-A248-93DC-DC4DEB917DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B61C93A-34B8-1E44-ABCD-B3A5517805EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2840" yWindow="3220" windowWidth="27240" windowHeight="16440" xr2:uid="{515AB8EB-AA8F-2C43-9A6B-8AF89862BE7B}"/>
+    <workbookView xWindow="2840" yWindow="3200" windowWidth="27240" windowHeight="16440" xr2:uid="{515AB8EB-AA8F-2C43-9A6B-8AF89862BE7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="3" r:id="rId1"/>
@@ -46,16 +46,16 @@
     <t>Make</t>
   </si>
   <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
     <t>VIN</t>
   </si>
   <si>
     <t>Date (YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>Model Name</t>
+  </si>
+  <si>
+    <t>Model Year</t>
   </si>
 </sst>
 </file>
@@ -441,6 +441,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC198ED0-26FB-CD41-B8E5-195ADA9EB37D}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -457,19 +460,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92E4EB6D-BD12-2541-B7A2-6CD22D531415}">
   <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="17.5" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -491,16 +500,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
